--- a/InputData/elec/BTaDLP/BAU Trans and Distr Loss Perc.xlsx
+++ b/InputData/elec/BTaDLP/BAU Trans and Distr Loss Perc.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26327"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\IA\elec\BTaDLP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-us\InputData\elec\BTaDLP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED17118-C5DD-426E-9868-E8802F35D698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A6FC856-0827-4238-87A9-5A3724A150AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3900" windowWidth="21600" windowHeight="12645" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19305" yWindow="-5760" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="MER 7.1" sheetId="2" r:id="rId2"/>
-    <sheet name="Calculations" sheetId="3" r:id="rId3"/>
-    <sheet name="BTaDLP" sheetId="4" r:id="rId4"/>
+    <sheet name="MER 7.1" sheetId="6" r:id="rId2"/>
+    <sheet name="Calculations" sheetId="4" r:id="rId3"/>
+    <sheet name="BTaDLP" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,13 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="36">
-  <si>
-    <t>BTaDLP BAU Transmission and Distribution Loss Percentage</t>
-  </si>
-  <si>
-    <t>Iowa</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="35">
   <si>
     <t>Source:</t>
   </si>
@@ -50,34 +43,16 @@
     <t>Energy Information Administration</t>
   </si>
   <si>
-    <t>April 2023 Monthly Energy Review</t>
+    <t>T&amp;D Losses and Unaccounted For</t>
   </si>
   <si>
-    <t>https://www.eia.gov/totalenergy/data/monthly/</t>
+    <t>Transmission and Distribution Loss Percentage</t>
   </si>
   <si>
-    <t>Table 7.1, Tab "Annual Data"</t>
-  </si>
-  <si>
-    <t>Notes:</t>
-  </si>
-  <si>
-    <t>This variable represents the percentage difference in generation</t>
-  </si>
-  <si>
-    <t>and delivered energy from the U.S. power system.</t>
+    <t>BTaDLP BAU Transmission and Distribution Loss Percentage</t>
   </si>
   <si>
     <t>U.S. Energy Information Administration</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Release Date: April 25, 2023</t>
-  </si>
-  <si>
-    <t>Next Update: May 25, 2023</t>
   </si>
   <si>
     <t>Table 7.1 Electricity Overview</t>
@@ -110,28 +85,16 @@
     <t>Transmission and Distribution Losses and Unaccounted for</t>
   </si>
   <si>
-    <t>Electricity Sales to Ultimate Customers</t>
-  </si>
-  <si>
     <t>Electricity Direct Use</t>
   </si>
   <si>
     <t>Electricity End Use, Total</t>
   </si>
   <si>
-    <t>(Billion Kilowatthours)</t>
-  </si>
-  <si>
     <t>Not Available</t>
   </si>
   <si>
-    <t>T&amp;D Losses and Unaccounted For</t>
-  </si>
-  <si>
     <t>Net Generation: Electric Power Sector</t>
-  </si>
-  <si>
-    <t>Transmission and Distribution Loss Percentage</t>
   </si>
   <si>
     <t>No meaningful trend since 2000, so we assume T&amp;D losses going forward are constant at the average value for this period.</t>
@@ -140,10 +103,43 @@
     <t>Average</t>
   </si>
   <si>
+    <t>Table 7.1, Tab "Annual Data"</t>
+  </si>
+  <si>
     <t>Year</t>
   </si>
   <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>This variable represents the percentage difference in generation</t>
+  </si>
+  <si>
+    <t>and delivered energy from the U.S. power system.</t>
+  </si>
+  <si>
     <t>Trans and Dist Loss Perc (dimensionless)</t>
+  </si>
+  <si>
+    <t>(Billion Kilowatthours)</t>
+  </si>
+  <si>
+    <t>https://www.eia.gov/totalenergy/data/monthly/</t>
+  </si>
+  <si>
+    <t>Electricity Sales to Ultimate Customers</t>
+  </si>
+  <si>
+    <t>April 2023 Monthly Energy Review</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Release Date: April 25, 2023</t>
+  </si>
+  <si>
+    <t>Next Update: May 25, 2023</t>
   </si>
 </sst>
 </file>
@@ -239,7 +235,7 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
@@ -270,7 +266,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Normal 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal 3" xfId="3" xr:uid="{A0D66D47-893E-4339-ABA2-2AA2E8FD27AB}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -308,11 +304,6 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
@@ -388,7 +379,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5D95-49D1-BBCA-AFEA06455242}"/>
+              <c16:uniqueId val="{00000000-8E0A-407E-88B4-8876B6204791}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -467,10 +458,10 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
+        <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -813,57 +804,54 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" s="2">
         <v>2023</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -871,18 +859,18 @@
     <hyperlink ref="B6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L86"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="9" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -896,9 +884,9 @@
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
     </row>
-    <row r="2" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A2" s="10" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -912,9 +900,9 @@
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -928,9 +916,9 @@
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -944,9 +932,9 @@
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -960,9 +948,9 @@
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
     </row>
-    <row r="9" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -976,81 +964,81 @@
       <c r="K9" s="8"/>
       <c r="L9" s="8"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="J11" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="K11" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="L11" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="K11" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="L11" s="13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="13"/>
       <c r="B12" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="14">
         <v>1949</v>
       </c>
@@ -1058,7 +1046,7 @@
         <v>291.10000000000002</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D13" s="8">
         <v>5.0250000000000004</v>
@@ -1082,13 +1070,13 @@
         <v>254.511</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L13" s="8">
         <v>254.511</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="14">
         <v>1950</v>
       </c>
@@ -1096,7 +1084,7 @@
         <v>329.14100000000002</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D14" s="8">
         <v>4.9459999999999997</v>
@@ -1120,13 +1108,13 @@
         <v>291.44299999999998</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L14" s="8">
         <v>291.44299999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="14">
         <v>1951</v>
       </c>
@@ -1134,7 +1122,7 @@
         <v>370.673</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D15" s="8">
         <v>4.6260000000000003</v>
@@ -1158,13 +1146,13 @@
         <v>330.28500000000003</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L15" s="8">
         <v>330.28500000000003</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="14">
         <v>1952</v>
       </c>
@@ -1172,7 +1160,7 @@
         <v>399.22399999999999</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D16" s="8">
         <v>4.6059999999999999</v>
@@ -1196,13 +1184,13 @@
         <v>356.16399999999999</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L16" s="8">
         <v>356.16399999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="14">
         <v>1953</v>
       </c>
@@ -1210,7 +1198,7 @@
         <v>442.66500000000002</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D17" s="8">
         <v>4.3840000000000003</v>
@@ -1234,13 +1222,13 @@
         <v>396.21699999999998</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L17" s="8">
         <v>396.21699999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" s="14">
         <v>1954</v>
       </c>
@@ -1248,7 +1236,7 @@
         <v>471.68599999999998</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D18" s="8">
         <v>4.5709999999999997</v>
@@ -1272,13 +1260,13 @@
         <v>424.16399999999999</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L18" s="8">
         <v>424.16399999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="14">
         <v>1955</v>
       </c>
@@ -1286,7 +1274,7 @@
         <v>547.03800000000001</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D19" s="8">
         <v>3.2610000000000001</v>
@@ -1310,13 +1298,13 @@
         <v>496.74799999999999</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L19" s="8">
         <v>496.74799999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" s="14">
         <v>1956</v>
       </c>
@@ -1324,7 +1312,7 @@
         <v>600.66800000000001</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D20" s="8">
         <v>3.2080000000000002</v>
@@ -1348,13 +1336,13 @@
         <v>546.28</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L20" s="8">
         <v>546.28</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" s="14">
         <v>1957</v>
       </c>
@@ -1362,7 +1350,7 @@
         <v>631.51700000000005</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D21" s="8">
         <v>3.125</v>
@@ -1386,13 +1374,13 @@
         <v>575.82000000000005</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L21" s="8">
         <v>575.82000000000005</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" s="14">
         <v>1958</v>
       </c>
@@ -1400,7 +1388,7 @@
         <v>645.09799999999996</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D22" s="8">
         <v>3.3519999999999999</v>
@@ -1424,13 +1412,13 @@
         <v>587.86300000000006</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L22" s="8">
         <v>587.86300000000006</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" s="14">
         <v>1959</v>
       </c>
@@ -1438,7 +1426,7 @@
         <v>710.00599999999997</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D23" s="8">
         <v>3.3730000000000002</v>
@@ -1462,13 +1450,13 @@
         <v>646.88800000000003</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L23" s="8">
         <v>646.88800000000003</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" s="14">
         <v>1960</v>
       </c>
@@ -1476,7 +1464,7 @@
         <v>755.54899999999998</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D24" s="8">
         <v>3.6070000000000002</v>
@@ -1500,13 +1488,13 @@
         <v>688.07500000000005</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L24" s="8">
         <v>688.07500000000005</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" s="14">
         <v>1961</v>
       </c>
@@ -1514,7 +1502,7 @@
         <v>793.76</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D25" s="8">
         <v>3.3650000000000002</v>
@@ -1538,13 +1526,13 @@
         <v>721.95</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L25" s="8">
         <v>721.95</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" s="14">
         <v>1962</v>
       </c>
@@ -1552,7 +1540,7 @@
         <v>854.53499999999997</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D26" s="8">
         <v>3.4089999999999998</v>
@@ -1576,13 +1564,13 @@
         <v>777.6</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L26" s="8">
         <v>777.6</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" s="14">
         <v>1963</v>
       </c>
@@ -1590,7 +1578,7 @@
         <v>916.79300000000001</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D27" s="8">
         <v>3.2349999999999999</v>
@@ -1614,13 +1602,13 @@
         <v>832.61300000000006</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L27" s="8">
         <v>832.61300000000006</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" s="14">
         <v>1964</v>
       </c>
@@ -1628,7 +1616,7 @@
         <v>983.99</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D28" s="8">
         <v>3.2280000000000002</v>
@@ -1652,13 +1640,13 @@
         <v>896.05899999999997</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L28" s="8">
         <v>896.05899999999997</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" s="14">
         <v>1965</v>
       </c>
@@ -1666,7 +1654,7 @@
         <v>1055.252</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D29" s="8">
         <v>3.1339999999999999</v>
@@ -1690,13 +1678,13 @@
         <v>953.78899999999999</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L29" s="8">
         <v>953.78899999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" s="14">
         <v>1966</v>
       </c>
@@ -1704,7 +1692,7 @@
         <v>1144.3499999999999</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D30" s="8">
         <v>3.1819999999999999</v>
@@ -1728,13 +1716,13 @@
         <v>1035.145</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L30" s="8">
         <v>1035.145</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" s="14">
         <v>1967</v>
       </c>
@@ -1742,7 +1730,7 @@
         <v>1214.365</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D31" s="8">
         <v>3.431</v>
@@ -1766,13 +1754,13 @@
         <v>1099.2170000000001</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L31" s="8">
         <v>1099.2170000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" s="14">
         <v>1968</v>
       </c>
@@ -1780,7 +1768,7 @@
         <v>1329.443</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D32" s="8">
         <v>3.383</v>
@@ -1804,13 +1792,13 @@
         <v>1202.8710000000001</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L32" s="8">
         <v>1202.8710000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="14">
         <v>1969</v>
       </c>
@@ -1818,7 +1806,7 @@
         <v>1442.182</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D33" s="8">
         <v>3.2759999999999998</v>
@@ -1842,13 +1830,13 @@
         <v>1313.8330000000001</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L33" s="8">
         <v>1313.8330000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="14">
         <v>1970</v>
       </c>
@@ -1856,7 +1844,7 @@
         <v>1531.8679999999999</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D34" s="8">
         <v>3.2440000000000002</v>
@@ -1880,13 +1868,13 @@
         <v>1392.3</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L34" s="8">
         <v>1392.3</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" s="14">
         <v>1971</v>
       </c>
@@ -1894,7 +1882,7 @@
         <v>1612.633</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D35" s="8">
         <v>3.2210000000000001</v>
@@ -1918,13 +1906,13 @@
         <v>1469.54</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L35" s="8">
         <v>1469.54</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" s="14">
         <v>1972</v>
       </c>
@@ -1932,7 +1920,7 @@
         <v>1749.662</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D36" s="8">
         <v>3.3159999999999998</v>
@@ -1956,13 +1944,13 @@
         <v>1595.1610000000001</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L36" s="8">
         <v>1595.1610000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" s="14">
         <v>1973</v>
       </c>
@@ -1970,7 +1958,7 @@
         <v>1860.71</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D37" s="8">
         <v>3.347</v>
@@ -1994,13 +1982,13 @@
         <v>1712.9090000000001</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L37" s="8">
         <v>1712.9090000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" s="14">
         <v>1974</v>
       </c>
@@ -2008,7 +1996,7 @@
         <v>1867.14</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D38" s="8">
         <v>3.18</v>
@@ -2032,13 +2020,13 @@
         <v>1705.924</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L38" s="8">
         <v>1705.924</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="14">
         <v>1975</v>
       </c>
@@ -2046,7 +2034,7 @@
         <v>1917.6489999999999</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D39" s="8">
         <v>3.1059999999999999</v>
@@ -2070,13 +2058,13 @@
         <v>1747.0909999999999</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L39" s="8">
         <v>1747.0909999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="14">
         <v>1976</v>
       </c>
@@ -2084,7 +2072,7 @@
         <v>2037.6959999999999</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D40" s="8">
         <v>3.2170000000000001</v>
@@ -2108,13 +2096,13 @@
         <v>1855.2460000000001</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L40" s="8">
         <v>1855.2460000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="14">
         <v>1977</v>
       </c>
@@ -2122,7 +2110,7 @@
         <v>2124.3229999999999</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D41" s="8">
         <v>3.1240000000000001</v>
@@ -2146,13 +2134,13 @@
         <v>1948.3610000000001</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L41" s="8">
         <v>1948.3610000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" s="14">
         <v>1978</v>
       </c>
@@ -2160,7 +2148,7 @@
         <v>2206.3310000000001</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D42" s="8">
         <v>3.0459999999999998</v>
@@ -2184,13 +2172,13 @@
         <v>2017.922</v>
       </c>
       <c r="K42" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L42" s="8">
         <v>2017.922</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="14">
         <v>1979</v>
       </c>
@@ -2198,7 +2186,7 @@
         <v>2247.3719999999998</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D43" s="8">
         <v>3.2930000000000001</v>
@@ -2222,13 +2210,13 @@
         <v>2071.0990000000002</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L43" s="8">
         <v>2071.0990000000002</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="14">
         <v>1980</v>
       </c>
@@ -2236,7 +2224,7 @@
         <v>2286.4389999999999</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D44" s="8">
         <v>3.161</v>
@@ -2260,13 +2248,13 @@
         <v>2094.4490000000001</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L44" s="8">
         <v>2094.4490000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" s="14">
         <v>1981</v>
       </c>
@@ -2274,7 +2262,7 @@
         <v>2294.8119999999999</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D45" s="8">
         <v>3.161</v>
@@ -2298,13 +2286,13 @@
         <v>2147.1030000000001</v>
       </c>
       <c r="K45" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L45" s="8">
         <v>2147.1030000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" s="14">
         <v>1982</v>
       </c>
@@ -2312,7 +2300,7 @@
         <v>2241.2109999999998</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D46" s="8">
         <v>3.161</v>
@@ -2336,13 +2324,13 @@
         <v>2086.4409999999998</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L46" s="8">
         <v>2086.4409999999998</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" s="14">
         <v>1983</v>
       </c>
@@ -2350,7 +2338,7 @@
         <v>2310.2849999999999</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D47" s="8">
         <v>3.161</v>
@@ -2374,13 +2362,13 @@
         <v>2150.9549999999999</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L47" s="8">
         <v>2150.9549999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="14">
         <v>1984</v>
       </c>
@@ -2388,7 +2376,7 @@
         <v>2416.3040000000001</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D48" s="8">
         <v>3.161</v>
@@ -2412,13 +2400,13 @@
         <v>2285.7959999999998</v>
       </c>
       <c r="K48" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L48" s="8">
         <v>2285.7959999999998</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" s="14">
         <v>1985</v>
       </c>
@@ -2426,7 +2414,7 @@
         <v>2469.8409999999999</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D49" s="8">
         <v>3.161</v>
@@ -2450,13 +2438,13 @@
         <v>2323.9740000000002</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L49" s="8">
         <v>2323.9740000000002</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" s="14">
         <v>1986</v>
       </c>
@@ -2464,7 +2452,7 @@
         <v>2487.31</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D50" s="8">
         <v>3.161</v>
@@ -2488,13 +2476,13 @@
         <v>2368.7530000000002</v>
       </c>
       <c r="K50" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L50" s="8">
         <v>2368.7530000000002</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" s="14">
         <v>1987</v>
       </c>
@@ -2502,7 +2490,7 @@
         <v>2572.127</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D51" s="8">
         <v>3.161</v>
@@ -2526,13 +2514,13 @@
         <v>2457.2719999999999</v>
       </c>
       <c r="K51" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L51" s="8">
         <v>2457.2719999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" s="14">
         <v>1988</v>
       </c>
@@ -2540,7 +2528,7 @@
         <v>2704.25</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D52" s="8">
         <v>3.161</v>
@@ -2564,13 +2552,13 @@
         <v>2578.0619999999999</v>
       </c>
       <c r="K52" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L52" s="8">
         <v>2578.0619999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" s="14">
         <v>1989</v>
       </c>
@@ -2608,7 +2596,7 @@
         <v>2755.6350000000002</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54" s="14">
         <v>1990</v>
       </c>
@@ -2646,7 +2634,7 @@
         <v>2837.0839999999998</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55" s="14">
         <v>1991</v>
       </c>
@@ -2684,7 +2672,7 @@
         <v>2886.06</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56" s="14">
         <v>1992</v>
       </c>
@@ -2722,7 +2710,7 @@
         <v>2897.2069999999999</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57" s="14">
         <v>1993</v>
       </c>
@@ -2760,7 +2748,7 @@
         <v>3000.7</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58" s="14">
         <v>1994</v>
       </c>
@@ -2798,7 +2786,7 @@
         <v>3080.8879999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A59" s="14">
         <v>1995</v>
       </c>
@@ -2836,7 +2824,7 @@
         <v>3163.9630000000002</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60" s="14">
         <v>1996</v>
       </c>
@@ -2874,7 +2862,7 @@
         <v>3253.7649999999999</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A61" s="14">
         <v>1997</v>
       </c>
@@ -2912,7 +2900,7 @@
         <v>3301.8490000000002</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A62" s="14">
         <v>1998</v>
       </c>
@@ -2950,7 +2938,7 @@
         <v>3425.0970000000002</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A63" s="14">
         <v>1999</v>
       </c>
@@ -2988,7 +2976,7 @@
         <v>3483.7159999999999</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A64" s="14">
         <v>2000</v>
       </c>
@@ -3026,7 +3014,7 @@
         <v>3592.357</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A65" s="14">
         <v>2001</v>
       </c>
@@ -3064,7 +3052,7 @@
         <v>3557.107</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A66" s="14">
         <v>2002</v>
       </c>
@@ -3102,7 +3090,7 @@
         <v>3631.65</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A67" s="14">
         <v>2003</v>
       </c>
@@ -3140,7 +3128,7 @@
         <v>3662.029</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A68" s="14">
         <v>2004</v>
       </c>
@@ -3178,7 +3166,7 @@
         <v>3715.9490000000001</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A69" s="14">
         <v>2005</v>
       </c>
@@ -3216,7 +3204,7 @@
         <v>3810.9839999999999</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A70" s="14">
         <v>2006</v>
       </c>
@@ -3254,7 +3242,7 @@
         <v>3816.8449999999998</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A71" s="14">
         <v>2007</v>
       </c>
@@ -3292,7 +3280,7 @@
         <v>3890.2310000000002</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A72" s="14">
         <v>2008</v>
       </c>
@@ -3330,7 +3318,7 @@
         <v>3866.1610000000001</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A73" s="14">
         <v>2009</v>
       </c>
@@ -3368,7 +3356,7 @@
         <v>3723.7330000000002</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A74" s="14">
         <v>2010</v>
       </c>
@@ -3406,7 +3394,7 @@
         <v>3886.752</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A75" s="14">
         <v>2011</v>
       </c>
@@ -3444,7 +3432,7 @@
         <v>3882.6</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A76" s="14">
         <v>2012</v>
       </c>
@@ -3482,7 +3470,7 @@
         <v>3832.306</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A77" s="14">
         <v>2013</v>
       </c>
@@ -3520,7 +3508,7 @@
         <v>3868.33</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A78" s="14">
         <v>2014</v>
       </c>
@@ -3558,7 +3546,7 @@
         <v>3903.2739999999999</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A79" s="14">
         <v>2015</v>
       </c>
@@ -3596,7 +3584,7 @@
         <v>3900.16</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A80" s="14">
         <v>2016</v>
       </c>
@@ -3634,7 +3622,7 @@
         <v>3902.2979999999998</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A81" s="14">
         <v>2017</v>
       </c>
@@ -3672,7 +3660,7 @@
         <v>3864.3150000000001</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A82" s="14">
         <v>2018</v>
       </c>
@@ -3710,7 +3698,7 @@
         <v>4003.0889999999999</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A83" s="14">
         <v>2019</v>
       </c>
@@ -3748,7 +3736,7 @@
         <v>3954.4209999999998</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A84" s="14">
         <v>2020</v>
       </c>
@@ -3786,7 +3774,7 @@
         <v>3856.377</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A85" s="14">
         <v>2021</v>
       </c>
@@ -3824,7 +3812,7 @@
         <v>3944.7890000000002</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A86" s="14">
         <v>2022</v>
       </c>
@@ -3863,6 +3851,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" display="http://www.eia.gov/totalenergy/data/monthly/dataunits.cfm" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
   </hyperlinks>
@@ -3873,26 +3862,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" customWidth="1"/>
-    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" customWidth="1"/>
+    <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.26953125" customWidth="1"/>
+    <col min="4" max="4" width="9.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>2000</v>
       </c>
@@ -3905,11 +3894,11 @@
         <v>3637.529</v>
       </c>
       <c r="D2" s="4">
-        <f t="shared" ref="D2:D24" si="0">B2/C2</f>
+        <f>B2/C2</f>
         <v>6.6944071098814603E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2001</v>
       </c>
@@ -3922,11 +3911,11 @@
         <v>3580.0529999999999</v>
       </c>
       <c r="D3" s="4">
-        <f t="shared" si="0"/>
+        <f>B3/C3</f>
         <v>5.6301959775455837E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>2002</v>
       </c>
@@ -3939,11 +3928,11 @@
         <v>3698.4580000000001</v>
       </c>
       <c r="D4" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D4:D8" si="0">B4/C4</f>
         <v>6.69968403047973E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2003</v>
       </c>
@@ -3960,7 +3949,7 @@
         <v>6.1157289973365822E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>2004</v>
       </c>
@@ -3977,7 +3966,7 @@
         <v>6.9824806478379145E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>2005</v>
       </c>
@@ -3994,7 +3983,7 @@
         <v>6.8991223394440859E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>2006</v>
       </c>
@@ -4011,7 +4000,7 @@
         <v>6.8135044422103247E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>2007</v>
       </c>
@@ -4024,11 +4013,11 @@
         <v>4005.3429999999998</v>
       </c>
       <c r="D9" s="4">
-        <f t="shared" si="0"/>
+        <f>B9/C9</f>
         <v>7.4342197409809851E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>2008</v>
       </c>
@@ -4041,11 +4030,11 @@
         <v>3974.3490000000002</v>
       </c>
       <c r="D10" s="4">
-        <f t="shared" si="0"/>
+        <f>B10/C10</f>
         <v>7.1973548372324628E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>2009</v>
       </c>
@@ -4058,11 +4047,11 @@
         <v>3809.837</v>
       </c>
       <c r="D11" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D11:D15" si="1">B11/C11</f>
         <v>6.8415000431776993E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>2010</v>
       </c>
@@ -4075,11 +4064,11 @@
         <v>3972.386</v>
       </c>
       <c r="D12" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.6530543607796436E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>2011</v>
       </c>
@@ -4092,11 +4081,11 @@
         <v>3948.1860000000001</v>
       </c>
       <c r="D13" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.4533940396931652E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>2012</v>
       </c>
@@ -4109,11 +4098,11 @@
         <v>3890.3580000000002</v>
       </c>
       <c r="D14" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.7531060123515632E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>2013</v>
       </c>
@@ -4126,11 +4115,11 @@
         <v>3903.7150000000001</v>
       </c>
       <c r="D15" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.5453036402503759E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>2014</v>
       </c>
@@ -4143,11 +4132,11 @@
         <v>3936.9609999999998</v>
       </c>
       <c r="D16" s="4">
-        <f t="shared" si="0"/>
+        <f>B16/C16</f>
         <v>6.1850244389009698E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>2015</v>
       </c>
@@ -4160,11 +4149,11 @@
         <v>3920.4070000000002</v>
       </c>
       <c r="D17" s="4">
-        <f t="shared" si="0"/>
+        <f>B17/C17</f>
         <v>6.2550648440327747E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>2016</v>
       </c>
@@ -4177,11 +4166,11 @@
         <v>3918.9769999999999</v>
       </c>
       <c r="D18" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D18:D21" si="2">B18/C18</f>
         <v>6.1694161512047659E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>2017</v>
       </c>
@@ -4194,11 +4183,11 @@
         <v>3878.625</v>
       </c>
       <c r="D19" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>5.8639853040703863E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>2018</v>
       </c>
@@ -4211,11 +4200,11 @@
         <v>4020.877</v>
       </c>
       <c r="D20" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>5.5300124823514867E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>2019</v>
       </c>
@@ -4228,11 +4217,11 @@
         <v>3968.348</v>
       </c>
       <c r="D21" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>5.4228610998833776E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>2020</v>
       </c>
@@ -4245,11 +4234,11 @@
         <v>3853.6559999999999</v>
       </c>
       <c r="D22" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D22:D23" si="3">B22/C22</f>
         <v>5.2081452002981067E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>2021</v>
       </c>
@@ -4262,11 +4251,11 @@
         <v>3957.181</v>
       </c>
       <c r="D23" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>5.160795020495651E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>2022</v>
       </c>
@@ -4279,18 +4268,18 @@
         <v>4090.28</v>
       </c>
       <c r="D24" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D24" si="4">B24/C24</f>
         <v>5.7715853193424413E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -4301,8 +4290,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -4312,15 +4301,15 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AK2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="20.453125" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B1">
         <v>2015</v>
@@ -4431,20 +4420,20 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:37" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:37" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B2" s="4">
         <f>Calculations!D28</f>
         <v>6.3165193947731083E-2</v>
       </c>
       <c r="C2" s="4">
-        <f t="shared" ref="C2:AK2" si="0">$B2</f>
+        <f>$B2</f>
         <v>6.3165193947731083E-2</v>
       </c>
       <c r="D2" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D2:AK2" si="0">$B2</f>
         <v>6.3165193947731083E-2</v>
       </c>
       <c r="E2" s="4">
